--- a/predictions_results_oos_sc25.xlsx
+++ b/predictions_results_oos_sc25.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M115"/>
+  <dimension ref="A1:K115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,30 +470,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Linear_Jpred</t>
+          <t>Forest_Delta_T_max</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Forest_Delta_T_max</t>
+          <t>Boosting_Delta_T_max</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Boosting_Delta_T_max</t>
+          <t>Jmax_parsed</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Linear_Delta_T_max</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Jmax_parsed</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>T_delta_SPE</t>
         </is>
@@ -521,12 +511,10 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="n">
+      <c r="J2" t="n">
         <v>66</v>
       </c>
-      <c r="M2" t="n">
+      <c r="K2" t="n">
         <v>19.33333333333333</v>
       </c>
     </row>
@@ -552,12 +540,10 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="n">
+      <c r="J3" t="n">
         <v>430</v>
       </c>
-      <c r="M3" t="n">
+      <c r="K3" t="n">
         <v>13</v>
       </c>
     </row>
@@ -583,12 +569,10 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="n">
+      <c r="J4" t="n">
         <v>860</v>
       </c>
-      <c r="M4" t="n">
+      <c r="K4" t="n">
         <v>19</v>
       </c>
     </row>
@@ -614,12 +598,10 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="n">
+      <c r="J5" t="n">
         <v>130</v>
       </c>
-      <c r="M5" t="n">
+      <c r="K5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -645,12 +627,10 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="n">
+      <c r="J6" t="n">
         <v>120</v>
       </c>
-      <c r="M6" t="n">
+      <c r="K6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -676,12 +656,10 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
+      <c r="J7" t="n">
         <v>96</v>
       </c>
-      <c r="M7" t="n">
+      <c r="K7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -707,12 +685,10 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="n">
+      <c r="J8" t="n">
         <v>22</v>
       </c>
-      <c r="M8" t="n">
+      <c r="K8" t="n">
         <v>36</v>
       </c>
     </row>
@@ -738,12 +714,10 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="n">
+      <c r="J9" t="n">
         <v>785</v>
       </c>
-      <c r="M9" t="n">
+      <c r="K9" t="n">
         <v>9</v>
       </c>
     </row>
@@ -769,12 +743,10 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
+      <c r="J10" t="n">
         <v>250</v>
       </c>
-      <c r="M10" t="n">
+      <c r="K10" t="n">
         <v>6</v>
       </c>
     </row>
@@ -800,12 +772,10 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="n">
-        <v>23</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="J11" t="n">
+        <v>23</v>
+      </c>
+      <c r="K11" t="n">
         <v>13</v>
       </c>
     </row>
@@ -831,12 +801,10 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="n">
+      <c r="J12" t="n">
         <v>20</v>
       </c>
-      <c r="M12" t="n">
+      <c r="K12" t="n">
         <v>4</v>
       </c>
     </row>
@@ -862,12 +830,10 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="n">
+      <c r="J13" t="n">
         <v>25</v>
       </c>
-      <c r="M13" t="n">
+      <c r="K13" t="n">
         <v>9</v>
       </c>
     </row>
@@ -893,12 +859,10 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="n">
+      <c r="J14" t="n">
         <v>54</v>
       </c>
-      <c r="M14" t="n">
+      <c r="K14" t="n">
         <v>34</v>
       </c>
     </row>
@@ -924,12 +888,10 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="n">
+      <c r="J15" t="n">
         <v>24</v>
       </c>
-      <c r="M15" t="n">
+      <c r="K15" t="n">
         <v>3</v>
       </c>
     </row>
@@ -955,12 +917,10 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="n">
+      <c r="J16" t="n">
         <v>7200</v>
       </c>
-      <c r="M16" t="n">
+      <c r="K16" t="n">
         <v>7</v>
       </c>
     </row>
@@ -986,12 +946,10 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="n">
+      <c r="J17" t="n">
         <v>13</v>
       </c>
-      <c r="M17" t="n">
+      <c r="K17" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1017,12 +975,10 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="n">
+      <c r="J18" t="n">
         <v>180</v>
       </c>
-      <c r="M18" t="n">
+      <c r="K18" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1048,12 +1004,10 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="n">
+      <c r="J19" t="n">
         <v>65</v>
       </c>
-      <c r="M19" t="n">
+      <c r="K19" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1079,12 +1033,10 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="n">
+      <c r="J20" t="n">
         <v>670</v>
       </c>
-      <c r="M20" t="n">
+      <c r="K20" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1110,12 +1062,10 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="n">
+      <c r="J21" t="n">
         <v>29</v>
       </c>
-      <c r="M21" t="n">
+      <c r="K21" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1141,12 +1091,10 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="n">
+      <c r="J22" t="n">
         <v>112</v>
       </c>
-      <c r="M22" t="n">
+      <c r="K22" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1172,12 +1120,10 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="n">
+      <c r="J23" t="n">
         <v>50</v>
       </c>
-      <c r="M23" t="n">
+      <c r="K23" t="n">
         <v>17</v>
       </c>
     </row>
@@ -1203,12 +1149,10 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="n">
+      <c r="J24" t="n">
         <v>270</v>
       </c>
-      <c r="M24" t="n">
+      <c r="K24" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1234,12 +1178,10 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="n">
+      <c r="J25" t="n">
         <v>190</v>
       </c>
-      <c r="M25" t="n">
+      <c r="K25" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1265,12 +1207,10 @@
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="n">
+      <c r="J26" t="n">
         <v>15</v>
       </c>
-      <c r="M26" t="n">
+      <c r="K26" t="n">
         <v>26</v>
       </c>
     </row>
@@ -1296,12 +1236,10 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="n">
+      <c r="J27" t="n">
         <v>390</v>
       </c>
-      <c r="M27" t="n">
+      <c r="K27" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1327,12 +1265,10 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="n">
+      <c r="J28" t="n">
         <v>370</v>
       </c>
-      <c r="M28" t="n">
+      <c r="K28" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1358,12 +1294,10 @@
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="n">
+      <c r="J29" t="n">
         <v>540</v>
       </c>
-      <c r="M29" t="n">
+      <c r="K29" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1389,12 +1323,10 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="n">
+      <c r="J30" t="n">
         <v>13</v>
       </c>
-      <c r="M30" t="n">
+      <c r="K30" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1420,12 +1352,10 @@
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="n">
+      <c r="J31" t="n">
         <v>336</v>
       </c>
-      <c r="M31" t="n">
+      <c r="K31" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1451,12 +1381,10 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="n">
+      <c r="J32" t="n">
         <v>40</v>
       </c>
-      <c r="M32" t="n">
+      <c r="K32" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1482,12 +1410,10 @@
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="n">
+      <c r="J33" t="n">
         <v>25.5</v>
       </c>
-      <c r="M33" t="n">
+      <c r="K33" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1513,12 +1439,10 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="n">
+      <c r="J34" t="n">
         <v>70</v>
       </c>
-      <c r="M34" t="n">
+      <c r="K34" t="n">
         <v>23</v>
       </c>
     </row>
@@ -1544,12 +1468,10 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="n">
+      <c r="J35" t="n">
         <v>14.5</v>
       </c>
-      <c r="M35" t="n">
+      <c r="K35" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1575,12 +1497,10 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="n">
+      <c r="J36" t="n">
         <v>21</v>
       </c>
-      <c r="M36" t="n">
+      <c r="K36" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1606,12 +1526,10 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="n">
+      <c r="J37" t="n">
         <v>915</v>
       </c>
-      <c r="M37" t="n">
+      <c r="K37" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1637,12 +1555,10 @@
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="n">
+      <c r="J38" t="n">
         <v>260</v>
       </c>
-      <c r="M38" t="n">
+      <c r="K38" t="n">
         <v>27</v>
       </c>
     </row>
@@ -1668,12 +1584,10 @@
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="n">
+      <c r="J39" t="n">
         <v>26</v>
       </c>
-      <c r="M39" t="n">
+      <c r="K39" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1699,12 +1613,10 @@
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="n">
+      <c r="J40" t="n">
         <v>27</v>
       </c>
-      <c r="M40" t="n">
+      <c r="K40" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1730,12 +1642,10 @@
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="n">
+      <c r="J41" t="n">
         <v>18.5</v>
       </c>
-      <c r="M41" t="n">
+      <c r="K41" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1761,12 +1671,10 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="n">
+      <c r="J42" t="n">
         <v>16</v>
       </c>
-      <c r="M42" t="n">
+      <c r="K42" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1792,12 +1700,10 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="n">
+      <c r="J43" t="n">
         <v>92</v>
       </c>
-      <c r="M43" t="n">
+      <c r="K43" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1823,12 +1729,10 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="n">
+      <c r="J44" t="n">
         <v>150</v>
       </c>
-      <c r="M44" t="n">
+      <c r="K44" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1854,12 +1758,10 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="n">
+      <c r="J45" t="n">
         <v>15.6</v>
       </c>
-      <c r="M45" t="n">
+      <c r="K45" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1885,12 +1787,10 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="n">
+      <c r="J46" t="n">
         <v>10.2</v>
       </c>
-      <c r="M46" t="n">
+      <c r="K46" t="n">
         <v>46</v>
       </c>
     </row>
@@ -1916,12 +1816,10 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="n">
+      <c r="J47" t="n">
         <v>230</v>
       </c>
-      <c r="M47" t="n">
+      <c r="K47" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1947,12 +1845,10 @@
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="n">
+      <c r="J48" t="n">
         <v>990</v>
       </c>
-      <c r="M48" t="n">
+      <c r="K48" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1978,12 +1874,10 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="n">
+      <c r="J49" t="n">
         <v>126</v>
       </c>
-      <c r="M49" t="n">
+      <c r="K49" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2009,12 +1903,10 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="n">
+      <c r="J50" t="n">
         <v>10.7</v>
       </c>
-      <c r="M50" t="n">
+      <c r="K50" t="n">
         <v>18</v>
       </c>
     </row>
@@ -2040,12 +1932,10 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="n">
+      <c r="J51" t="n">
         <v>21</v>
       </c>
-      <c r="M51" t="n">
+      <c r="K51" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2071,12 +1961,10 @@
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="n">
+      <c r="J52" t="n">
         <v>13</v>
       </c>
-      <c r="M52" t="n">
+      <c r="K52" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2102,12 +1990,10 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="n">
+      <c r="J53" t="n">
         <v>27</v>
       </c>
-      <c r="M53" t="n">
+      <c r="K53" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2133,12 +2019,10 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="n">
+      <c r="J54" t="n">
         <v>210</v>
       </c>
-      <c r="M54" t="n">
+      <c r="K54" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2164,12 +2048,10 @@
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="n">
+      <c r="J55" t="n">
         <v>46</v>
       </c>
-      <c r="M55" t="n">
+      <c r="K55" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2195,12 +2077,10 @@
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="n">
+      <c r="J56" t="n">
         <v>54</v>
       </c>
-      <c r="M56" t="n">
+      <c r="K56" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2226,12 +2106,10 @@
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="n">
+      <c r="J57" t="n">
         <v>264</v>
       </c>
-      <c r="M57" t="n">
+      <c r="K57" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2257,12 +2135,10 @@
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="n">
+      <c r="J58" t="n">
         <v>330</v>
       </c>
-      <c r="M58" t="n">
+      <c r="K58" t="n">
         <v>18</v>
       </c>
     </row>
@@ -2288,12 +2164,10 @@
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="n">
+      <c r="J59" t="n">
         <v>134</v>
       </c>
-      <c r="M59" t="n">
+      <c r="K59" t="n">
         <v>34</v>
       </c>
     </row>
@@ -2319,12 +2193,10 @@
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="n">
+      <c r="J60" t="n">
         <v>41</v>
       </c>
-      <c r="M60" t="n">
+      <c r="K60" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2350,12 +2222,10 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="n">
+      <c r="J61" t="n">
         <v>130</v>
       </c>
-      <c r="M61" t="n">
+      <c r="K61" t="n">
         <v>13</v>
       </c>
     </row>
@@ -2381,12 +2251,10 @@
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="n">
+      <c r="J62" t="n">
         <v>12</v>
       </c>
-      <c r="M62" t="n">
+      <c r="K62" t="n">
         <v>4</v>
       </c>
     </row>
@@ -2412,12 +2280,10 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="n">
+      <c r="J63" t="n">
         <v>280</v>
       </c>
-      <c r="M63" t="n">
+      <c r="K63" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2443,12 +2309,10 @@
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="n">
+      <c r="J64" t="n">
         <v>70</v>
       </c>
-      <c r="M64" t="n">
+      <c r="K64" t="n">
         <v>23</v>
       </c>
     </row>
@@ -2474,12 +2338,10 @@
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="n">
+      <c r="J65" t="n">
         <v>160</v>
       </c>
-      <c r="M65" t="n">
+      <c r="K65" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2505,12 +2367,10 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="n">
+      <c r="J66" t="n">
         <v>660</v>
       </c>
-      <c r="M66" t="n">
+      <c r="K66" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2536,12 +2396,10 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="n">
+      <c r="J67" t="n">
         <v>160</v>
       </c>
-      <c r="M67" t="n">
+      <c r="K67" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2567,12 +2425,10 @@
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="n">
+      <c r="J68" t="n">
         <v>45</v>
       </c>
-      <c r="M68" t="n">
+      <c r="K68" t="n">
         <v>7</v>
       </c>
     </row>
@@ -2598,12 +2454,10 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="n">
+      <c r="J69" t="n">
         <v>2700</v>
       </c>
-      <c r="M69" t="n">
+      <c r="K69" t="n">
         <v>37</v>
       </c>
     </row>
@@ -2629,12 +2483,10 @@
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="n">
+      <c r="J70" t="n">
         <v>740</v>
       </c>
-      <c r="M70" t="n">
+      <c r="K70" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2660,12 +2512,10 @@
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="n">
+      <c r="J71" t="n">
         <v>1440</v>
       </c>
-      <c r="M71" t="n">
+      <c r="K71" t="n">
         <v>35</v>
       </c>
     </row>
@@ -2691,12 +2541,10 @@
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="n">
+      <c r="J72" t="n">
         <v>180</v>
       </c>
-      <c r="M72" t="n">
+      <c r="K72" t="n">
         <v>24</v>
       </c>
     </row>
@@ -2722,12 +2570,10 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="n">
+      <c r="J73" t="n">
         <v>11</v>
       </c>
-      <c r="M73" t="n">
+      <c r="K73" t="n">
         <v>51</v>
       </c>
     </row>
@@ -2753,12 +2599,10 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="n">
-        <v>23</v>
-      </c>
-      <c r="M74" t="n">
+      <c r="J74" t="n">
+        <v>23</v>
+      </c>
+      <c r="K74" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2784,12 +2628,10 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="n">
+      <c r="J75" t="n">
         <v>17</v>
       </c>
-      <c r="M75" t="n">
+      <c r="K75" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2815,12 +2657,10 @@
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="n">
+      <c r="J76" t="n">
         <v>93</v>
       </c>
-      <c r="M76" t="n">
+      <c r="K76" t="n">
         <v>9</v>
       </c>
     </row>
@@ -2846,12 +2686,10 @@
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="n">
+      <c r="J77" t="n">
         <v>75</v>
       </c>
-      <c r="M77" t="n">
+      <c r="K77" t="n">
         <v>21</v>
       </c>
     </row>
@@ -2877,12 +2715,10 @@
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="n">
+      <c r="J78" t="n">
         <v>1000</v>
       </c>
-      <c r="M78" t="n">
+      <c r="K78" t="n">
         <v>18</v>
       </c>
     </row>
@@ -2908,12 +2744,10 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="n">
+      <c r="J79" t="n">
         <v>25</v>
       </c>
-      <c r="M79" t="n">
+      <c r="K79" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2939,12 +2773,10 @@
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="n">
+      <c r="J80" t="n">
         <v>230</v>
       </c>
-      <c r="M80" t="n">
+      <c r="K80" t="n">
         <v>18</v>
       </c>
     </row>
@@ -2970,12 +2802,10 @@
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="n">
+      <c r="J81" t="n">
         <v>13.5</v>
       </c>
-      <c r="M81" t="n">
+      <c r="K81" t="n">
         <v>25</v>
       </c>
     </row>
@@ -3001,12 +2831,10 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="n">
+      <c r="J82" t="n">
         <v>99</v>
       </c>
-      <c r="M82" t="n">
+      <c r="K82" t="n">
         <v>10</v>
       </c>
     </row>
@@ -3032,12 +2860,10 @@
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="n">
+      <c r="J83" t="n">
         <v>39</v>
       </c>
-      <c r="M83" t="n">
+      <c r="K83" t="n">
         <v>17</v>
       </c>
     </row>
@@ -3063,12 +2889,10 @@
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="n">
+      <c r="J84" t="n">
         <v>575</v>
       </c>
-      <c r="M84" t="n">
+      <c r="K84" t="n">
         <v>4</v>
       </c>
     </row>
@@ -3097,21 +2921,15 @@
         <v>87.49234594095377</v>
       </c>
       <c r="H85" t="n">
-        <v>82.30005861740167</v>
+        <v>10.82</v>
       </c>
       <c r="I85" t="n">
-        <v>10.82</v>
+        <v>7.51496706177756</v>
       </c>
       <c r="J85" t="n">
-        <v>7.51496706177756</v>
+        <v>15.56</v>
       </c>
       <c r="K85" t="n">
-        <v>12.45241235133906</v>
-      </c>
-      <c r="L85" t="n">
-        <v>15.56</v>
-      </c>
-      <c r="M85" t="n">
         <v>3.666666666666667</v>
       </c>
     </row>
@@ -3140,21 +2958,15 @@
         <v>73.73011573679341</v>
       </c>
       <c r="H86" t="n">
-        <v>89.12288663643398</v>
+        <v>3.79</v>
       </c>
       <c r="I86" t="n">
-        <v>3.79</v>
+        <v>2.703202290961086</v>
       </c>
       <c r="J86" t="n">
-        <v>2.703202290961086</v>
+        <v>22.42</v>
       </c>
       <c r="K86" t="n">
-        <v>12.34345153875393</v>
-      </c>
-      <c r="L86" t="n">
-        <v>22.42</v>
-      </c>
-      <c r="M86" t="n">
         <v>3.833333333333333</v>
       </c>
     </row>
@@ -3183,21 +2995,15 @@
         <v>39.14437597130733</v>
       </c>
       <c r="H87" t="n">
-        <v>85.71545994450791</v>
+        <v>5.64</v>
       </c>
       <c r="I87" t="n">
-        <v>5.64</v>
+        <v>7.267808684988984</v>
       </c>
       <c r="J87" t="n">
-        <v>7.267808684988984</v>
+        <v>22.7</v>
       </c>
       <c r="K87" t="n">
-        <v>12.39155620719444</v>
-      </c>
-      <c r="L87" t="n">
-        <v>22.7</v>
-      </c>
-      <c r="M87" t="n">
         <v>3.583333333333333</v>
       </c>
     </row>
@@ -3226,21 +3032,15 @@
         <v>92.33197833686344</v>
       </c>
       <c r="H88" t="n">
-        <v>84.82873006825844</v>
+        <v>7.09</v>
       </c>
       <c r="I88" t="n">
-        <v>7.09</v>
+        <v>5.533352027388157</v>
       </c>
       <c r="J88" t="n">
-        <v>5.533352027388157</v>
+        <v>18.1</v>
       </c>
       <c r="K88" t="n">
-        <v>12.38171161743646</v>
-      </c>
-      <c r="L88" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="M88" t="n">
         <v>1.666666666666667</v>
       </c>
     </row>
@@ -3269,21 +3069,15 @@
         <v>289.6267690238853</v>
       </c>
       <c r="H89" t="n">
-        <v>90.57410034414639</v>
+        <v>6.666666666666666</v>
       </c>
       <c r="I89" t="n">
-        <v>6.666666666666666</v>
+        <v>5.486299643494523</v>
       </c>
       <c r="J89" t="n">
-        <v>5.486299643494523</v>
+        <v>10.6</v>
       </c>
       <c r="K89" t="n">
-        <v>12.40930411366767</v>
-      </c>
-      <c r="L89" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="M89" t="n">
         <v>12</v>
       </c>
     </row>
@@ -3312,21 +3106,15 @@
         <v>28.77363545802731</v>
       </c>
       <c r="H90" t="n">
-        <v>84.90462840682694</v>
+        <v>3.91</v>
       </c>
       <c r="I90" t="n">
-        <v>3.91</v>
+        <v>3.115885522452154</v>
       </c>
       <c r="J90" t="n">
-        <v>3.115885522452154</v>
+        <v>32.2</v>
       </c>
       <c r="K90" t="n">
-        <v>12.36524784575578</v>
-      </c>
-      <c r="L90" t="n">
-        <v>32.2</v>
-      </c>
-      <c r="M90" t="n">
         <v>2.416666666666667</v>
       </c>
     </row>
@@ -3355,21 +3143,15 @@
         <v>33.50818847824586</v>
       </c>
       <c r="H91" t="n">
-        <v>81.97757430037831</v>
+        <v>11.61</v>
       </c>
       <c r="I91" t="n">
-        <v>11.61</v>
+        <v>14.71368394434598</v>
       </c>
       <c r="J91" t="n">
-        <v>14.71368394434598</v>
+        <v>27.5</v>
       </c>
       <c r="K91" t="n">
-        <v>12.79007924571372</v>
-      </c>
-      <c r="L91" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="M91" t="n">
         <v>6.333333333333333</v>
       </c>
     </row>
@@ -3398,21 +3180,15 @@
         <v>31.34106145752704</v>
       </c>
       <c r="H92" t="n">
-        <v>85.40548326736767</v>
+        <v>11.01</v>
       </c>
       <c r="I92" t="n">
-        <v>11.01</v>
+        <v>15.51980304679877</v>
       </c>
       <c r="J92" t="n">
-        <v>15.51980304679877</v>
+        <v>36.26</v>
       </c>
       <c r="K92" t="n">
-        <v>12.49566509307724</v>
-      </c>
-      <c r="L92" t="n">
-        <v>36.26</v>
-      </c>
-      <c r="M92" t="n">
         <v>1.583333333333333</v>
       </c>
     </row>
@@ -3441,21 +3217,15 @@
         <v>28.18815490687476</v>
       </c>
       <c r="H93" t="n">
-        <v>79.93401129539049</v>
+        <v>21.45</v>
       </c>
       <c r="I93" t="n">
-        <v>21.45</v>
+        <v>19.53139965327548</v>
       </c>
       <c r="J93" t="n">
-        <v>19.53139965327548</v>
+        <v>38.4</v>
       </c>
       <c r="K93" t="n">
-        <v>12.78427175334393</v>
-      </c>
-      <c r="L93" t="n">
-        <v>38.4</v>
-      </c>
-      <c r="M93" t="n">
         <v>23.83333333333333</v>
       </c>
     </row>
@@ -3484,21 +3254,15 @@
         <v>46.56547861413619</v>
       </c>
       <c r="H94" t="n">
-        <v>82.35356739277442</v>
+        <v>10.24</v>
       </c>
       <c r="I94" t="n">
-        <v>10.24</v>
+        <v>7.151527030913045</v>
       </c>
       <c r="J94" t="n">
-        <v>7.151527030913045</v>
+        <v>40</v>
       </c>
       <c r="K94" t="n">
-        <v>12.69161953318451</v>
-      </c>
-      <c r="L94" t="n">
-        <v>40</v>
-      </c>
-      <c r="M94" t="n">
         <v>5.083333333333333</v>
       </c>
     </row>
@@ -3527,21 +3291,15 @@
         <v>256.417802080313</v>
       </c>
       <c r="H95" t="n">
-        <v>82.32524479666421</v>
+        <v>7.95</v>
       </c>
       <c r="I95" t="n">
-        <v>7.95</v>
+        <v>7.414537846854851</v>
       </c>
       <c r="J95" t="n">
-        <v>7.414537846854851</v>
+        <v>18</v>
       </c>
       <c r="K95" t="n">
-        <v>12.39191644012277</v>
-      </c>
-      <c r="L95" t="n">
-        <v>18</v>
-      </c>
-      <c r="M95" t="n">
         <v>1.916666666666667</v>
       </c>
     </row>
@@ -3570,21 +3328,15 @@
         <v>63.98991925435622</v>
       </c>
       <c r="H96" t="n">
-        <v>83.04488760981287</v>
+        <v>8.68</v>
       </c>
       <c r="I96" t="n">
-        <v>8.68</v>
+        <v>8.479591929431846</v>
       </c>
       <c r="J96" t="n">
-        <v>8.479591929431846</v>
+        <v>614</v>
       </c>
       <c r="K96" t="n">
-        <v>12.49502302568096</v>
-      </c>
-      <c r="L96" t="n">
-        <v>614</v>
-      </c>
-      <c r="M96" t="n">
         <v>6.083333333333333</v>
       </c>
     </row>
@@ -3613,21 +3365,15 @@
         <v>48.17640365047234</v>
       </c>
       <c r="H97" t="n">
-        <v>84.20097110923926</v>
+        <v>9.19</v>
       </c>
       <c r="I97" t="n">
-        <v>9.19</v>
+        <v>6.981282505934099</v>
       </c>
       <c r="J97" t="n">
-        <v>6.981282505934099</v>
+        <v>153</v>
       </c>
       <c r="K97" t="n">
-        <v>12.46322380990492</v>
-      </c>
-      <c r="L97" t="n">
-        <v>153</v>
-      </c>
-      <c r="M97" t="n">
         <v>16.08333333333333</v>
       </c>
     </row>
@@ -3656,21 +3402,15 @@
         <v>38.80267294657376</v>
       </c>
       <c r="H98" t="n">
-        <v>81.97824569320198</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="I98" t="n">
-        <v>8.279999999999999</v>
+        <v>8.483318835077112</v>
       </c>
       <c r="J98" t="n">
-        <v>8.483318835077112</v>
+        <v>17.4</v>
       </c>
       <c r="K98" t="n">
-        <v>12.54054184187348</v>
-      </c>
-      <c r="L98" t="n">
-        <v>17.4</v>
-      </c>
-      <c r="M98" t="n">
         <v>5.583333333333333</v>
       </c>
     </row>
@@ -3699,21 +3439,15 @@
         <v>146.6206297027424</v>
       </c>
       <c r="H99" t="n">
-        <v>92.82717361379869</v>
+        <v>7.036666666666666</v>
       </c>
       <c r="I99" t="n">
-        <v>7.036666666666666</v>
+        <v>6.436270576563408</v>
       </c>
       <c r="J99" t="n">
-        <v>6.436270576563408</v>
+        <v>17.7</v>
       </c>
       <c r="K99" t="n">
-        <v>12.39122324240363</v>
-      </c>
-      <c r="L99" t="n">
-        <v>17.7</v>
-      </c>
-      <c r="M99" t="n">
         <v>3</v>
       </c>
     </row>
@@ -3742,21 +3476,15 @@
         <v>147.2026173990332</v>
       </c>
       <c r="H100" t="n">
-        <v>92.67946346516771</v>
+        <v>3.786666666666666</v>
       </c>
       <c r="I100" t="n">
-        <v>3.786666666666666</v>
+        <v>4.265630396169238</v>
       </c>
       <c r="J100" t="n">
-        <v>4.265630396169238</v>
+        <v>27.2</v>
       </c>
       <c r="K100" t="n">
-        <v>12.33150233331905</v>
-      </c>
-      <c r="L100" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="M100" t="n">
         <v>8.5</v>
       </c>
     </row>
@@ -3785,21 +3513,15 @@
         <v>65.8366721058775</v>
       </c>
       <c r="H101" t="n">
-        <v>82.0900015300595</v>
+        <v>6.85</v>
       </c>
       <c r="I101" t="n">
-        <v>6.85</v>
+        <v>7.51496706177756</v>
       </c>
       <c r="J101" t="n">
-        <v>7.51496706177756</v>
+        <v>25.85</v>
       </c>
       <c r="K101" t="n">
-        <v>12.48162759872384</v>
-      </c>
-      <c r="L101" t="n">
-        <v>25.85</v>
-      </c>
-      <c r="M101" t="n">
         <v>2.25</v>
       </c>
     </row>
@@ -3828,21 +3550,15 @@
         <v>127.3610919439789</v>
       </c>
       <c r="H102" t="n">
-        <v>70.82571987417458</v>
+        <v>18.2</v>
       </c>
       <c r="I102" t="n">
-        <v>18.2</v>
+        <v>17.18958850016933</v>
       </c>
       <c r="J102" t="n">
-        <v>17.18958850016933</v>
+        <v>18.4</v>
       </c>
       <c r="K102" t="n">
-        <v>14.05505554109791</v>
-      </c>
-      <c r="L102" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="M102" t="n">
         <v>53.5</v>
       </c>
     </row>
@@ -3871,21 +3587,15 @@
         <v>29.31392458547525</v>
       </c>
       <c r="H103" t="n">
-        <v>86.6567511029818</v>
+        <v>12.49333333333333</v>
       </c>
       <c r="I103" t="n">
-        <v>12.49333333333333</v>
+        <v>13.91418157422962</v>
       </c>
       <c r="J103" t="n">
-        <v>13.91418157422962</v>
+        <v>16.3</v>
       </c>
       <c r="K103" t="n">
-        <v>12.38106327051773</v>
-      </c>
-      <c r="L103" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="M103" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3914,21 +3624,15 @@
         <v>358.5017266877167</v>
       </c>
       <c r="H104" t="n">
-        <v>107.1974716029882</v>
+        <v>12.2</v>
       </c>
       <c r="I104" t="n">
-        <v>12.2</v>
+        <v>8.547150564127209</v>
       </c>
       <c r="J104" t="n">
-        <v>8.547150564127209</v>
+        <v>113</v>
       </c>
       <c r="K104" t="n">
-        <v>12.31631139329049</v>
-      </c>
-      <c r="L104" t="n">
-        <v>113</v>
-      </c>
-      <c r="M104" t="n">
         <v>4.416666666666667</v>
       </c>
     </row>
@@ -3957,21 +3661,15 @@
         <v>15.59978005837832</v>
       </c>
       <c r="H105" t="n">
-        <v>83.21562332835266</v>
+        <v>17.03</v>
       </c>
       <c r="I105" t="n">
-        <v>17.03</v>
+        <v>24.94888002560824</v>
       </c>
       <c r="J105" t="n">
-        <v>24.94888002560824</v>
+        <v>96</v>
       </c>
       <c r="K105" t="n">
-        <v>12.76183086713682</v>
-      </c>
-      <c r="L105" t="n">
-        <v>96</v>
-      </c>
-      <c r="M105" t="n">
         <v>14</v>
       </c>
     </row>
@@ -4000,21 +3698,15 @@
         <v>213.2839794712957</v>
       </c>
       <c r="H106" t="n">
-        <v>79.53144340220054</v>
+        <v>20.83</v>
       </c>
       <c r="I106" t="n">
-        <v>20.83</v>
+        <v>22.31512164767092</v>
       </c>
       <c r="J106" t="n">
-        <v>22.31512164767092</v>
+        <v>16.7</v>
       </c>
       <c r="K106" t="n">
-        <v>12.75815651448595</v>
-      </c>
-      <c r="L106" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="M106" t="n">
         <v>0.8333333333333334</v>
       </c>
     </row>
@@ -4043,21 +3735,15 @@
         <v>109.8430101139548</v>
       </c>
       <c r="H107" t="n">
-        <v>87.23871511781434</v>
+        <v>11.10333333333334</v>
       </c>
       <c r="I107" t="n">
-        <v>11.10333333333334</v>
+        <v>7.540629333636151</v>
       </c>
       <c r="J107" t="n">
-        <v>7.540629333636151</v>
+        <v>956</v>
       </c>
       <c r="K107" t="n">
-        <v>12.63189108867298</v>
-      </c>
-      <c r="L107" t="n">
-        <v>956</v>
-      </c>
-      <c r="M107" t="n">
         <v>14.33333333333333</v>
       </c>
     </row>
@@ -4086,21 +3772,15 @@
         <v>1378.707462229089</v>
       </c>
       <c r="H108" t="n">
-        <v>130.2842413310401</v>
+        <v>10.92333333333333</v>
       </c>
       <c r="I108" t="n">
-        <v>10.92333333333333</v>
+        <v>7.868420276639233</v>
       </c>
       <c r="J108" t="n">
-        <v>7.868420276639233</v>
+        <v>116</v>
       </c>
       <c r="K108" t="n">
-        <v>12.18215610395038</v>
-      </c>
-      <c r="L108" t="n">
-        <v>116</v>
-      </c>
-      <c r="M108" t="n">
         <v>7.333333333333333</v>
       </c>
     </row>
@@ -4129,21 +3809,15 @@
         <v>32.8981305039887</v>
       </c>
       <c r="H109" t="n">
-        <v>84.78702073170774</v>
+        <v>12.89</v>
       </c>
       <c r="I109" t="n">
-        <v>12.89</v>
+        <v>15.64606875933494</v>
       </c>
       <c r="J109" t="n">
-        <v>15.64606875933494</v>
+        <v>121</v>
       </c>
       <c r="K109" t="n">
-        <v>12.58314937645416</v>
-      </c>
-      <c r="L109" t="n">
-        <v>121</v>
-      </c>
-      <c r="M109" t="n">
         <v>18</v>
       </c>
     </row>
@@ -4172,21 +3846,15 @@
         <v>73.73011573679341</v>
       </c>
       <c r="H110" t="n">
-        <v>89.09449303753162</v>
+        <v>7.87</v>
       </c>
       <c r="I110" t="n">
-        <v>7.87</v>
+        <v>5.713385713090546</v>
       </c>
       <c r="J110" t="n">
-        <v>5.713385713090546</v>
+        <v>1029</v>
       </c>
       <c r="K110" t="n">
-        <v>12.33150735693702</v>
-      </c>
-      <c r="L110" t="n">
-        <v>1029</v>
-      </c>
-      <c r="M110" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4215,21 +3883,15 @@
         <v>34.0443484664801</v>
       </c>
       <c r="H111" t="n">
-        <v>78.48015700154656</v>
+        <v>41.98</v>
       </c>
       <c r="I111" t="n">
-        <v>41.98</v>
+        <v>50.12407413584049</v>
       </c>
       <c r="J111" t="n">
-        <v>50.12407413584049</v>
+        <v>34</v>
       </c>
       <c r="K111" t="n">
-        <v>12.93664362668344</v>
-      </c>
-      <c r="L111" t="n">
-        <v>34</v>
-      </c>
-      <c r="M111" t="n">
         <v>16.83333333333333</v>
       </c>
     </row>
@@ -4258,21 +3920,15 @@
         <v>280.7293716347093</v>
       </c>
       <c r="H112" t="n">
-        <v>94.2077763168387</v>
+        <v>10.42333333333334</v>
       </c>
       <c r="I112" t="n">
-        <v>10.42333333333334</v>
+        <v>6.436270576563408</v>
       </c>
       <c r="J112" t="n">
-        <v>6.436270576563408</v>
+        <v>1040</v>
       </c>
       <c r="K112" t="n">
-        <v>12.39525657207835</v>
-      </c>
-      <c r="L112" t="n">
-        <v>1040</v>
-      </c>
-      <c r="M112" t="n">
         <v>10.16666666666667</v>
       </c>
     </row>
@@ -4301,21 +3957,15 @@
         <v>26.16077946410907</v>
       </c>
       <c r="H113" t="n">
-        <v>74.2948743116612</v>
+        <v>10.52</v>
       </c>
       <c r="I113" t="n">
-        <v>10.52</v>
+        <v>9.834076806374277</v>
       </c>
       <c r="J113" t="n">
-        <v>9.834076806374277</v>
+        <v>364</v>
       </c>
       <c r="K113" t="n">
-        <v>15.89300703985838</v>
-      </c>
-      <c r="L113" t="n">
-        <v>364</v>
-      </c>
-      <c r="M113" t="n">
         <v>76.83333333333333</v>
       </c>
     </row>
@@ -4344,21 +3994,15 @@
         <v>26.58571386900402</v>
       </c>
       <c r="H114" t="n">
-        <v>81.451839997924</v>
+        <v>7.22</v>
       </c>
       <c r="I114" t="n">
-        <v>7.22</v>
+        <v>7.51496706177756</v>
       </c>
       <c r="J114" t="n">
-        <v>7.51496706177756</v>
+        <v>18.3</v>
       </c>
       <c r="K114" t="n">
-        <v>12.54115601317999</v>
-      </c>
-      <c r="L114" t="n">
-        <v>18.3</v>
-      </c>
-      <c r="M114" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4387,21 +4031,15 @@
         <v>38.80267294657376</v>
       </c>
       <c r="H115" t="n">
-        <v>81.82704045794394</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="I115" t="n">
-        <v>8.369999999999999</v>
+        <v>8.483318835077112</v>
       </c>
       <c r="J115" t="n">
-        <v>8.483318835077112</v>
+        <v>37.1</v>
       </c>
       <c r="K115" t="n">
-        <v>12.55135644020058</v>
-      </c>
-      <c r="L115" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="M115" t="n">
         <v>3.666666666666667</v>
       </c>
     </row>
